--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104601_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104601_W16.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2408</v>
+        <v>4.5242</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5682</v>
+        <v>2.6185</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6726</v>
+        <v>1.9057</v>
       </c>
       <c r="G2" t="n">
-        <v>1.6429</v>
+        <v>1.6474</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5656</v>
+        <v>1.5653</v>
       </c>
       <c r="I2" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1629</v>
+        <v>1.1576</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1256</v>
+        <v>1.1204</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M2" t="n">
-        <v>0.48</v>
+        <v>0.4898</v>
       </c>
       <c r="N2" t="n">
-        <v>0.44</v>
+        <v>0.4449</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1442</v>
+        <v>0.4215</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3126</v>
+        <v>0.3714</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1685</v>
+        <v>0.0501</v>
       </c>
       <c r="V2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1039</v>
+        <v>4.1545</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5416</v>
+        <v>2.1442</v>
       </c>
       <c r="F3" t="n">
-        <v>1.5623</v>
+        <v>2.0103</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8592</v>
+        <v>1.8564</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7344000000000001</v>
+        <v>0.7379</v>
       </c>
       <c r="I3" t="n">
-        <v>1.1248</v>
+        <v>1.1184</v>
       </c>
       <c r="J3" t="n">
-        <v>2.8335</v>
+        <v>2.7976</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4533</v>
+        <v>0.4374</v>
       </c>
       <c r="L3" t="n">
-        <v>2.3802</v>
+        <v>2.3602</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.9743000000000001</v>
+        <v>-0.9412</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2811</v>
+        <v>0.3005</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.2554</v>
+        <v>-1.2417</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>3.6293</v>
+        <v>3.6421</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.6231</v>
+        <v>-1.5621</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5303</v>
+        <v>-0.8715000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.0927</v>
+        <v>-0.6906</v>
       </c>
       <c r="V3" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. RAIESTE</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.483</v>
+        <v>1.9989</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4743</v>
+        <v>1.1424</v>
       </c>
       <c r="F4" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.8566</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1312</v>
+        <v>2.3755</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0261</v>
+        <v>-0.4854</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1573</v>
+        <v>2.8609</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2282</v>
+        <v>1.9302</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1487</v>
+        <v>-0.3555</v>
       </c>
       <c r="L4" t="n">
-        <v>1.0795</v>
+        <v>2.2857</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0971</v>
+        <v>0.4452</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1749</v>
+        <v>-0.13</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9222</v>
+        <v>0.5752</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2683</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2683</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1762</v>
+        <v>0.0999</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2461</v>
+        <v>0.1925</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0699</v>
+        <v>-0.0926</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.0927</v>
+        <v>-0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.937</v>
+        <v>1.9273</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1229</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>3.0599</v>
+        <v>2.5608</v>
       </c>
       <c r="G5" t="n">
-        <v>3.7729</v>
+        <v>3.7683</v>
       </c>
       <c r="H5" t="n">
-        <v>3.0131</v>
+        <v>2.9992</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7598</v>
+        <v>0.7691</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7482</v>
+        <v>3.7202</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4794</v>
+        <v>2.4541</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2688</v>
+        <v>1.2661</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0247</v>
+        <v>0.0481</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5337</v>
+        <v>0.5451</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.509</v>
+        <v>-0.497</v>
       </c>
       <c r="P5" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3378</v>
+        <v>0.3474</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8166</v>
+        <v>-0.2744</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1544</v>
+        <v>0.6218</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="W5" t="n">
-        <v>0.4822</v>
+        <v>0.4733</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>H. SANT-ROOS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8417</v>
+        <v>1.8734</v>
       </c>
       <c r="E6" t="n">
-        <v>1.9664</v>
+        <v>1.6678</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1247</v>
+        <v>0.2056</v>
       </c>
       <c r="G6" t="n">
-        <v>0.3192</v>
+        <v>2.4879</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.635</v>
+        <v>2.8436</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9542</v>
+        <v>-0.3557</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2699</v>
+        <v>1.8819</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.6651</v>
+        <v>2.4854</v>
       </c>
       <c r="L6" t="n">
-        <v>1.9351</v>
+        <v>-0.6035</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9507</v>
+        <v>0.606</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0301</v>
+        <v>0.3583</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9808</v>
+        <v>0.2477</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0415</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.519</v>
+        <v>-0.5933</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3962</v>
+        <v>-0.3232</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1228</v>
+        <v>-0.2702</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>H. SANT-ROOS</t>
+          <t>S. RAIESTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.604</v>
+        <v>1.4744</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2763</v>
+        <v>1.401</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3277</v>
+        <v>0.07340000000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>2.486</v>
+        <v>0.1402</v>
       </c>
       <c r="H7" t="n">
-        <v>2.8485</v>
+        <v>-0.0177</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3625</v>
+        <v>0.1579</v>
       </c>
       <c r="J7" t="n">
-        <v>1.904</v>
+        <v>1.2133</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5038</v>
+        <v>0.1411</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5998</v>
+        <v>1.0722</v>
       </c>
       <c r="M7" t="n">
-        <v>0.582</v>
+        <v>-1.0731</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3446</v>
+        <v>-0.1588</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2373</v>
+        <v>-0.9143</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>2.2763</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>2.2763</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8574000000000001</v>
+        <v>0.1473</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.747</v>
+        <v>0.1877</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1104</v>
+        <v>-0.0403</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2534</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1853</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.4214</v>
+        <v>1.4408</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5896</v>
+        <v>1.6605</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8318</v>
+        <v>-0.2197</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3897</v>
+        <v>0.3236</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.4863</v>
+        <v>-0.6266</v>
       </c>
       <c r="I8" t="n">
-        <v>2.876</v>
+        <v>0.9502</v>
       </c>
       <c r="J8" t="n">
-        <v>1.9623</v>
+        <v>1.252</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.3432</v>
+        <v>-0.669</v>
       </c>
       <c r="L8" t="n">
-        <v>2.3055</v>
+        <v>1.921</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4274</v>
+        <v>-0.9284</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1431</v>
+        <v>0.0424</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5705</v>
+        <v>-0.9708</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4537</v>
+        <v>2.0487</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.49</v>
+        <v>-0.9315</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3992</v>
+        <v>-0.6808999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0907</v>
+        <v>-0.2505</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9320000000000001</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.984</v>
+        <v>-1.3207</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4714</v>
+        <v>-0.1472</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4554</v>
+        <v>-1.1736</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4009</v>
+        <v>-0.3957</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.0086</v>
+        <v>-1.0081</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6078</v>
+        <v>0.6124000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1389</v>
+        <v>0.1195</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6447000000000001</v>
+        <v>-0.6625</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5397999999999999</v>
+        <v>-0.5152</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3639</v>
+        <v>-0.3457</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1759</v>
+        <v>-0.1695</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4924</v>
+        <v>-0.834</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5989</v>
+        <v>0.0112</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0912</v>
+        <v>-0.8452</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W9" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6891</v>
+        <v>-3.3148</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.1778</v>
+        <v>-3.6106</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4887</v>
+        <v>0.2958</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.217</v>
+        <v>-2.2197</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5772</v>
+        <v>-1.5714</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6398</v>
+        <v>-0.6484</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.4872</v>
+        <v>-2.507</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.4342</v>
+        <v>-1.4414</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.053</v>
+        <v>-1.0656</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2701</v>
+        <v>0.2873</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4455</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5565</v>
+        <v>0.0346</v>
       </c>
       <c r="U10" t="n">
-        <v>0.111</v>
+        <v>-0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.9379</v>
+        <v>-5.3821</v>
       </c>
       <c r="E11" t="n">
-        <v>-7.0555</v>
+        <v>-6.6795</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1176</v>
+        <v>1.2975</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.9719</v>
+        <v>-4.9635</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.4965</v>
+        <v>-0.4887</v>
       </c>
       <c r="I11" t="n">
-        <v>-4.4754</v>
+        <v>-4.4748</v>
       </c>
       <c r="J11" t="n">
-        <v>-4.1741</v>
+        <v>-4.2094</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5407999999999999</v>
+        <v>-0.5591</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.6333</v>
+        <v>-3.6503</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7978</v>
+        <v>-0.7541</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0443</v>
+        <v>0.0704</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8421999999999999</v>
+        <v>-0.8245</v>
       </c>
       <c r="P11" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>3.4025</v>
+        <v>3.4145</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3289</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9345</v>
+        <v>-0.5094</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3944</v>
+        <v>-0.2734</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.7712</v>
+        <v>-0.7739</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.0208</v>
+        <v>7.375900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4683999999999999</v>
+        <v>-0.4364999999999997</v>
       </c>
       <c r="F12" t="n">
-        <v>7.489199999999999</v>
+        <v>7.812399999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>5.0113</v>
+        <v>5.020400000000002</v>
       </c>
       <c r="H12" t="n">
-        <v>3.931900000000002</v>
+        <v>3.948100000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0795</v>
+        <v>1.0721</v>
       </c>
       <c r="J12" t="n">
-        <v>7.5866</v>
+        <v>7.355900000000003</v>
       </c>
       <c r="K12" t="n">
-        <v>3.082800000000001</v>
+        <v>2.9509</v>
       </c>
       <c r="L12" t="n">
-        <v>4.504</v>
+        <v>4.404999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.5755</v>
+        <v>-2.335599999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>0.8488000000000001</v>
+        <v>0.9971000000000002</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.4245</v>
+        <v>-3.3327</v>
       </c>
       <c r="P12" t="n">
-        <v>7.9391</v>
+        <v>7.9672</v>
       </c>
       <c r="Q12" t="n">
-        <v>-13.6101</v>
+        <v>-13.658</v>
       </c>
       <c r="R12" t="n">
-        <v>21.5491</v>
+        <v>21.6251</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.098100000000001</v>
+        <v>-3.763</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.2227</v>
+        <v>-1.862</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.8752</v>
+        <v>-1.9009</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.8316</v>
+        <v>-1.8484</v>
       </c>
       <c r="W12" t="n">
-        <v>7.777699999999999</v>
+        <v>7.7276</v>
       </c>
       <c r="X12" t="n">
-        <v>-9.609200000000001</v>
+        <v>-9.576099999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6047</v>
+        <v>5.8848</v>
       </c>
       <c r="E13" t="n">
-        <v>3.4762</v>
+        <v>3.523</v>
       </c>
       <c r="F13" t="n">
-        <v>2.1284</v>
+        <v>2.3618</v>
       </c>
       <c r="G13" t="n">
-        <v>5.4957</v>
+        <v>5.4719</v>
       </c>
       <c r="H13" t="n">
-        <v>4.4402</v>
+        <v>4.4266</v>
       </c>
       <c r="I13" t="n">
-        <v>1.0555</v>
+        <v>1.0453</v>
       </c>
       <c r="J13" t="n">
-        <v>5.7932</v>
+        <v>5.7381</v>
       </c>
       <c r="K13" t="n">
-        <v>3.6396</v>
+        <v>3.609</v>
       </c>
       <c r="L13" t="n">
-        <v>2.1535</v>
+        <v>2.1291</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.2975</v>
+        <v>-0.2662</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8006</v>
+        <v>0.8176</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.0981</v>
+        <v>-1.0838</v>
       </c>
       <c r="P13" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q13" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4382</v>
+        <v>0.7469</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0998</v>
+        <v>0.0205</v>
       </c>
       <c r="U13" t="n">
-        <v>0.538</v>
+        <v>0.7264</v>
       </c>
       <c r="V13" t="n">
-        <v>2.1659</v>
+        <v>2.17</v>
       </c>
       <c r="W13" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5269</v>
+        <v>0.5358000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.4384</v>
+        <v>1.2957</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1322</v>
+        <v>0.7662</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3062</v>
+        <v>0.5294</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6296</v>
+        <v>-0.6168</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0128</v>
+        <v>0.0252</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6424</v>
+        <v>-0.642</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.0361</v>
+        <v>-0.0464</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1559</v>
+        <v>0.1551</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.192</v>
+        <v>-0.2015</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5935</v>
+        <v>-0.5704</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.1431</v>
+        <v>-0.13</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P14" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>0.7906</v>
+        <v>0.6271</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5293</v>
+        <v>0.1784</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2613</v>
+        <v>0.4487</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.08359999999999999</v>
+        <v>-0.0804</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.1763</v>
+        <v>-1.1698</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SPISSU</t>
+          <t>Y. TRAORE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4529</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1006</v>
+        <v>0.5427</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3523</v>
+        <v>0.1705</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.4015</v>
+        <v>0.2572</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4228</v>
+        <v>-0.5684</v>
       </c>
       <c r="I15" t="n">
-        <v>0.0213</v>
+        <v>0.8256</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.614</v>
+        <v>-0.0169</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0835</v>
+        <v>-0.1659</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5306</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.7875</v>
+        <v>0.2741</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3393</v>
+        <v>-0.4025</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5518999999999999</v>
+        <v>0.6766</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.6276</v>
+        <v>0.4681</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7561</v>
+        <v>0.7872</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1286</v>
+        <v>-0.3191</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5463</v>
+        <v>-0.4673</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5463</v>
+        <v>-0.4673</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>M. SPISSU</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3963</v>
+        <v>0.3401</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9957</v>
+        <v>-0.047</v>
       </c>
       <c r="F16" t="n">
-        <v>1.392</v>
+        <v>0.3871</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0863</v>
+        <v>-1.3997</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.3504</v>
+        <v>-1.419</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4368</v>
+        <v>0.0193</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1652</v>
+        <v>-0.6412</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.6633</v>
+        <v>-0.0969</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8285</v>
+        <v>-0.5443</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.0789</v>
+        <v>-0.7585</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3129</v>
+        <v>-1.3221</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3918</v>
+        <v>0.5636</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2268</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.361</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5878</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4688</v>
+        <v>0.5122</v>
       </c>
       <c r="T16" t="n">
-        <v>0.0393</v>
+        <v>0.6429</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4294</v>
+        <v>-0.1308</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3856</v>
+        <v>0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Y. TRAORE</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.307</v>
+        <v>-0.0027</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4351</v>
+        <v>-1.2691</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1281</v>
+        <v>1.2663</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2557</v>
+        <v>0.0798</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.5627</v>
+        <v>-1.3608</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8184</v>
+        <v>1.4406</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0035</v>
+        <v>0.1344</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1527</v>
+        <v>-1.6902</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1493</v>
+        <v>1.8246</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2592</v>
+        <v>-0.0546</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4099</v>
+        <v>0.3294</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6691</v>
+        <v>-0.384</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6805</v>
+        <v>1.5934</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0668</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6654</v>
+        <v>-0.1955</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5985</v>
+        <v>0.2722</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.4692</v>
+        <v>-0.387</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.4692</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>M. GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.3943</v>
+        <v>-0.4991</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.8967</v>
+        <v>0.2875</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5024</v>
+        <v>-0.7866</v>
       </c>
       <c r="G18" t="n">
-        <v>0.399</v>
+        <v>-0.8928</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4965</v>
+        <v>-0.1467</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8955</v>
+        <v>-0.746</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1305</v>
+        <v>-0.609</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.274</v>
+        <v>-0.7207</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4045</v>
+        <v>0.1117</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7316</v>
+        <v>-0.2838</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2225</v>
+        <v>0.574</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.509</v>
+        <v>-0.8578</v>
       </c>
       <c r="P18" t="n">
-        <v>-3.4025</v>
+        <v>0.4553</v>
       </c>
       <c r="Q18" t="n">
-        <v>-5.8976</v>
+        <v>-0.2276</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>1.2787</v>
+        <v>1.0279</v>
       </c>
       <c r="T18" t="n">
-        <v>0.617</v>
+        <v>0.0346</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6617</v>
+        <v>0.9933</v>
       </c>
       <c r="V18" t="n">
-        <v>1.3305</v>
+        <v>-1.0895</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2534</v>
+        <v>1.0895</v>
       </c>
       <c r="X18" t="n">
-        <v>0.0771</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. GONZALEZ</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8257</v>
+        <v>-0.9043</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2958</v>
+        <v>-3.196</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.53</v>
+        <v>2.2916</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.9032</v>
+        <v>0.391</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1516</v>
+        <v>-0.4887</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7516</v>
+        <v>0.8797</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6051</v>
+        <v>1.0901</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.7171</v>
+        <v>-0.2865</v>
       </c>
       <c r="L19" t="n">
-        <v>0.112</v>
+        <v>1.3767</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2981</v>
+        <v>-0.6992</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5655</v>
+        <v>-0.2022</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8636</v>
+        <v>-0.497</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4537</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2268</v>
+        <v>-5.9184</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6805</v>
+        <v>2.5039</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7165</v>
+        <v>0.7945</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5565</v>
+        <v>0.3851</v>
       </c>
       <c r="U19" t="n">
-        <v>1.273</v>
+        <v>0.4094</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0927</v>
+        <v>1.3246</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1853</v>
+        <v>0.0774</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3806</v>
+        <v>-2.1342</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.2428</v>
+        <v>-2.2061</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1378</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.2105</v>
+        <v>-0.2089</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1702</v>
+        <v>-1.1744</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9596</v>
+        <v>0.9655</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8747</v>
+        <v>-0.8843</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.9493</v>
+        <v>-0.9588</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6641</v>
+        <v>0.6754</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O20" t="n">
-        <v>0.885</v>
+        <v>0.8911</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S20" t="n">
-        <v>2.327</v>
+        <v>1.5771</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9417</v>
+        <v>1.0031</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3853</v>
+        <v>0.574</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.4141</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.4035</v>
+        <v>-2.2039</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.3305</v>
+        <v>-0.3313</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.073</v>
+        <v>-1.8727</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.123</v>
+        <v>-1.1156</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.534</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1404</v>
+        <v>-1.1328</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5891</v>
+        <v>-0.5868</v>
       </c>
       <c r="P21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6415</v>
+        <v>-0.4542</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3478</v>
+        <v>-0.3485</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2937</v>
+        <v>-0.1057</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.365</v>
+        <v>-3.2777</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8164</v>
+        <v>-0.7176</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.5485</v>
+        <v>-2.5601</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5724</v>
+        <v>-2.5729</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.6853</v>
+        <v>-0.6918</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.8871</v>
+        <v>-1.8811</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.4271</v>
+        <v>-0.4389</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4644</v>
+        <v>-0.4761</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.1453</v>
+        <v>-2.134</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.9245</v>
+        <v>-1.9184</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1781</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3478</v>
+        <v>-0.2301</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1697</v>
+        <v>0.1383</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2534</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.8509</v>
+        <v>-5.4495</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.0553</v>
+        <v>-5.1647</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.7956</v>
+        <v>-0.2848</v>
       </c>
       <c r="G23" t="n">
-        <v>-4.4076</v>
+        <v>-4.4135</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.0113</v>
+        <v>-2.0214</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3963</v>
+        <v>-2.3921</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9702</v>
+        <v>-2.0076</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3574</v>
+        <v>-0.3834</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.6127</v>
+        <v>-1.6242</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.4374</v>
+        <v>-2.4059</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6539</v>
+        <v>-1.638</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7835</v>
+        <v>-0.768</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.8562</v>
+        <v>-3.8697</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.7965</v>
+        <v>-0.3834</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.3217</v>
+        <v>-0.3768</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4748</v>
+        <v>-0.0066</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3947</v>
+        <v>1.3961</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X23" t="n">
-        <v>0.302</v>
+        <v>0.3066</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.020700000000001</v>
+        <v>-6.237599999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-7.489100000000001</v>
+        <v>-7.8124</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4683000000000005</v>
+        <v>1.5745</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.0111</v>
+        <v>-5.0203</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.9318</v>
+        <v>-3.948100000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.079399999999999</v>
+        <v>-1.072</v>
       </c>
       <c r="J24" t="n">
-        <v>2.575499999999998</v>
+        <v>2.3355</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.8488999999999995</v>
+        <v>-0.9971999999999996</v>
       </c>
       <c r="L24" t="n">
-        <v>3.4244</v>
+        <v>3.332700000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>-7.5869</v>
+        <v>-7.355899999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.0828</v>
+        <v>-2.9512</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.504</v>
+        <v>-4.405</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.9392</v>
+        <v>-7.967000000000001</v>
       </c>
       <c r="Q24" t="n">
-        <v>-21.5492</v>
+        <v>-21.625</v>
       </c>
       <c r="R24" t="n">
-        <v>13.6101</v>
+        <v>13.658</v>
       </c>
       <c r="S24" t="n">
-        <v>4.0981</v>
+        <v>4.9012</v>
       </c>
       <c r="T24" t="n">
-        <v>1.8752</v>
+        <v>1.9009</v>
       </c>
       <c r="U24" t="n">
-        <v>2.2228</v>
+        <v>3.0001</v>
       </c>
       <c r="V24" t="n">
-        <v>1.8315</v>
+        <v>1.8484</v>
       </c>
       <c r="W24" t="n">
-        <v>9.609300000000001</v>
+        <v>9.576199999999998</v>
       </c>
       <c r="X24" t="n">
-        <v>-7.7776</v>
+        <v>-7.727300000000001</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104601_W16.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104601_W16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,7 @@
       <c r="X12" t="n">
         <v>-9.576099999999999</v>
       </c>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1541,11 @@
       <c r="X13" t="n">
         <v>0.5358000000000001</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.1698</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.4673</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.0774</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0.3066</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104601_W16.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-7.727300000000001</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
